--- a/results/naming/naming.xlsx
+++ b/results/naming/naming.xlsx
@@ -1032,7 +1032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1109,40 +1109,40 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="D2" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="E2" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6</v>
+        <v>2.2</v>
       </c>
       <c r="G2" t="n">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="I2" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J2" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="K2" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="L2" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
       <c r="M2" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="3">
@@ -1152,40 +1152,40 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="C3" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="D3" t="n">
         <v>1.1</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G3" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="H3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="I3" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="J3" t="n">
         <v>0.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="M3" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="4">
@@ -1198,37 +1198,37 @@
         <v>0.4</v>
       </c>
       <c r="C4" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="D4" t="n">
         <v>1.1</v>
       </c>
       <c r="E4" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="F4" t="n">
         <v>0.2</v>
       </c>
       <c r="G4" t="n">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="I4" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="L4" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="M4" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -1238,40 +1238,40 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="D5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="E5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="F5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="G5" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="I5" t="n">
         <v>2.7</v>
       </c>
-      <c r="C5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="D5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F5" t="n">
+      <c r="J5" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" t="n">
         <v>3.2</v>
       </c>
-      <c r="G5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="I5" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="J5" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="L5" t="n">
-        <v>3.4</v>
-      </c>
       <c r="M5" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="6">
@@ -1281,7 +1281,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="C6" t="n">
         <v>0.3</v>
@@ -1302,7 +1302,7 @@
         <v>0.5</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="J6" t="n">
         <v>0.2</v>
@@ -1324,40 +1324,40 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="I7" t="n">
         <v>3.3</v>
       </c>
-      <c r="F7" t="n">
-        <v>4</v>
-      </c>
-      <c r="G7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>3.5</v>
-      </c>
       <c r="J7" t="n">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="K7" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="M7" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="8">
@@ -1367,40 +1367,40 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="C8" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="D8" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="E8" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="F8" t="n">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="G8" t="n">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="H8" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="I8" t="n">
-        <v>11.5</v>
+        <v>10.9</v>
       </c>
       <c r="J8" t="n">
-        <v>4.5</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="L8" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="M8" t="n">
-        <v>9.5</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="9">
@@ -1410,31 +1410,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="C9" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="D9" t="n">
         <v>0.5</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G9" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="H9" t="n">
         <v>0.5</v>
       </c>
       <c r="I9" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="K9" t="n">
         <v>1.1</v>
@@ -1443,7 +1443,7 @@
         <v>0.4</v>
       </c>
       <c r="M9" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="10">
@@ -1453,40 +1453,40 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="C10" t="n">
         <v>0.7</v>
       </c>
       <c r="D10" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="E10" t="n">
-        <v>2.9</v>
+        <v>2.7</v>
       </c>
       <c r="F10" t="n">
-        <v>4.8</v>
+        <v>4.1</v>
       </c>
       <c r="G10" t="n">
         <v>0.7</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="I10" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J10" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="K10" t="n">
         <v>1.2</v>
       </c>
       <c r="L10" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="M10" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="11">
@@ -1496,40 +1496,40 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="C11" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="D11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="F11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G11" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I11" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
         <v>1.4</v>
       </c>
-      <c r="E11" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="F11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="I11" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="J11" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K11" t="n">
-        <v>1.5</v>
-      </c>
       <c r="L11" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="M11" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="12">
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="C12" t="n">
         <v>0.8</v>
@@ -1548,10 +1548,10 @@
         <v>0.5</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G12" t="n">
         <v>0.8</v>
@@ -1563,16 +1563,16 @@
         <v>1.5</v>
       </c>
       <c r="J12" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="M12" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="13">
@@ -1582,40 +1582,40 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>6.4</v>
+        <v>5.3</v>
       </c>
       <c r="C13" t="n">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="D13" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="E13" t="n">
-        <v>12.9</v>
+        <v>11.9</v>
       </c>
       <c r="F13" t="n">
-        <v>6.3</v>
+        <v>5.4</v>
       </c>
       <c r="G13" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="H13" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="I13" t="n">
-        <v>12.4</v>
+        <v>11.7</v>
       </c>
       <c r="J13" t="n">
-        <v>6.6</v>
+        <v>5.3</v>
       </c>
       <c r="K13" t="n">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="L13" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="M13" t="n">
-        <v>11.1</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="14">
@@ -1628,28 +1628,28 @@
         <v>0.1</v>
       </c>
       <c r="C14" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="D14" t="n">
         <v>0.1</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="G14" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="I14" t="n">
         <v>0.8</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
         <v>0.8</v>
@@ -1658,7 +1658,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="15">
@@ -1668,34 +1668,34 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="C15" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="E15" t="n">
         <v>0.2</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="G15" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="H15" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="I15" t="n">
         <v>0.3</v>
       </c>
       <c r="J15" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K15" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="L15" t="n">
         <v>0.5</v>
@@ -1711,40 +1711,40 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="C16" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="D16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="E16" t="n">
         <v>2.7</v>
       </c>
-      <c r="E16" t="n">
-        <v>3</v>
-      </c>
       <c r="F16" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="G16" t="n">
         <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="M16" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="17">
@@ -1754,40 +1754,40 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6.8</v>
+        <v>5.6</v>
       </c>
       <c r="C17" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="D17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="E17" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F17" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="I17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="J17" t="n">
         <v>4.1</v>
       </c>
-      <c r="E17" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="F17" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="G17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="I17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J17" t="n">
-        <v>5.2</v>
-      </c>
       <c r="K17" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="L17" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="18">
@@ -1797,19 +1797,19 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="C18" t="n">
         <v>0.4</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="E18" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="F18" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="G18" t="n">
         <v>0.2</v>
@@ -1818,10 +1818,10 @@
         <v>0.8</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J18" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="K18" t="n">
         <v>0.1</v>
@@ -1830,7 +1830,7 @@
         <v>0.5</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="19">
@@ -1840,40 +1840,40 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="C19" t="n">
-        <v>9.6</v>
+        <v>9.1</v>
       </c>
       <c r="D19" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="E19" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="G19" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="H19" t="n">
-        <v>11.3</v>
+        <v>10.7</v>
       </c>
       <c r="I19" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="K19" t="n">
-        <v>8.199999999999999</v>
+        <v>7.7</v>
       </c>
       <c r="L19" t="n">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="M19" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1883,40 +1883,40 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.7</v>
+        <v>5.5</v>
       </c>
       <c r="C20" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="D20" t="n">
-        <v>21.4</v>
+        <v>20.1</v>
       </c>
       <c r="E20" t="n">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="F20" t="n">
-        <v>7.4</v>
+        <v>6.3</v>
       </c>
       <c r="G20" t="n">
-        <v>10.6</v>
+        <v>10.3</v>
       </c>
       <c r="H20" t="n">
-        <v>23.1</v>
+        <v>21.9</v>
       </c>
       <c r="I20" t="n">
-        <v>8.4</v>
+        <v>7.9</v>
       </c>
       <c r="J20" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="K20" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="L20" t="n">
-        <v>20.6</v>
+        <v>19.4</v>
       </c>
       <c r="M20" t="n">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="21">
@@ -1926,40 +1926,40 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="C21" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="D21" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="E21" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="F21" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="G21" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="H21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L21" t="n">
         <v>2.3</v>
       </c>
-      <c r="I21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="J21" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L21" t="n">
-        <v>2.4</v>
-      </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="22">
@@ -1969,40 +1969,40 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>10.4</v>
+        <v>8.6</v>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="E22" t="n">
-        <v>6.7</v>
+        <v>6.2</v>
       </c>
       <c r="F22" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="G22" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="H22" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
       <c r="I22" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="J22" t="n">
-        <v>13.7</v>
+        <v>11</v>
       </c>
       <c r="K22" t="n">
-        <v>9.1</v>
+        <v>8.5</v>
       </c>
       <c r="L22" t="n">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
       <c r="M22" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="23">
@@ -2012,40 +2012,40 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="D23" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="E23" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="F23" t="n">
-        <v>5.5</v>
+        <v>4.7</v>
       </c>
       <c r="G23" t="n">
         <v>1.6</v>
       </c>
       <c r="H23" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="I23" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
-        <v>5.8</v>
+        <v>4.7</v>
       </c>
       <c r="K23" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="L23" t="n">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="M23" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="24">
@@ -2055,7 +2055,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="C24" t="n">
         <v>0.9</v>
@@ -2067,7 +2067,7 @@
         <v>0.5</v>
       </c>
       <c r="F24" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="G24" t="n">
         <v>0.8</v>
@@ -2079,10 +2079,10 @@
         <v>0.3</v>
       </c>
       <c r="J24" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="K24" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="L24" t="n">
         <v>0.2</v>
@@ -2098,34 +2098,34 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="C25" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="D25" t="n">
         <v>1.1</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="F25" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="G25" t="n">
         <v>0.8</v>
       </c>
       <c r="H25" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="I25" t="n">
         <v>0.5</v>
       </c>
       <c r="J25" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="K25" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="L25" t="n">
         <v>0.8</v>
@@ -2141,40 +2141,40 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
       <c r="C26" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="D26" t="n">
-        <v>8.1</v>
+        <v>7.6</v>
       </c>
       <c r="E26" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="F26" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G26" t="n">
         <v>1.9</v>
       </c>
       <c r="H26" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="I26" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J26" t="n">
-        <v>4.3</v>
+        <v>3.4</v>
       </c>
       <c r="K26" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="L26" t="n">
-        <v>10.2</v>
+        <v>9.6</v>
       </c>
       <c r="M26" t="n">
-        <v>5.4</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="27">
@@ -2184,19 +2184,19 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
       <c r="C27" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D27" t="n">
         <v>1.8</v>
       </c>
-      <c r="D27" t="n">
-        <v>1.9</v>
-      </c>
       <c r="E27" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="F27" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="G27" t="n">
         <v>1.1</v>
@@ -2208,16 +2208,16 @@
         <v>0.7</v>
       </c>
       <c r="J27" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="K27" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="L27" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="M27" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2227,40 +2227,40 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="C28" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="D28" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="E28" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="F28" t="n">
-        <v>7.1</v>
+        <v>6.1</v>
       </c>
       <c r="G28" t="n">
         <v>2.1</v>
       </c>
       <c r="H28" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J28" t="n">
-        <v>7</v>
+        <v>5.6</v>
       </c>
       <c r="K28" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L28" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="M28" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="29">
@@ -2270,40 +2270,40 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="D29" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="E29" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="F29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I29" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L29" t="n">
         <v>2.6</v>
       </c>
-      <c r="G29" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H29" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="I29" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K29" t="n">
-        <v>4</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>2.7</v>
-      </c>
-      <c r="M29" t="n">
-        <v>2.9</v>
       </c>
     </row>
     <row r="30">
@@ -2313,40 +2313,40 @@
         </is>
       </c>
       <c r="B30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" t="n">
         <v>2.4</v>
       </c>
-      <c r="C30" t="n">
-        <v>2.5</v>
-      </c>
       <c r="D30" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="E30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="I30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J30" t="n">
         <v>2.4</v>
       </c>
-      <c r="F30" t="n">
+      <c r="K30" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="L30" t="n">
         <v>2.2</v>
       </c>
-      <c r="G30" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H30" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="I30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J30" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K30" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="L30" t="n">
-        <v>2.3</v>
-      </c>
       <c r="M30" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="31">
@@ -2359,16 +2359,16 @@
         <v>0.3</v>
       </c>
       <c r="C31" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="D31" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="E31" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="F31" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="G31" t="n">
         <v>0.5</v>
@@ -2380,13 +2380,13 @@
         <v>0.3</v>
       </c>
       <c r="J31" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="K31" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="L31" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="M31" t="n">
         <v>0.3</v>
@@ -2399,19 +2399,19 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="C32" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="D32" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="E32" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="F32" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G32" t="n">
         <v>0.6</v>
@@ -2420,19 +2420,19 @@
         <v>1</v>
       </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J32" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="K32" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="L32" t="n">
         <v>0.7</v>
       </c>
       <c r="M32" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="33">
@@ -2442,7 +2442,7 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="C33" t="n">
         <v>0.1</v>
@@ -2451,7 +2451,7 @@
         <v>0.1</v>
       </c>
       <c r="E33" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="F33" t="n">
         <v>0.1</v>
@@ -2466,7 +2466,7 @@
         <v>0.1</v>
       </c>
       <c r="J33" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="n">
         <v>0</v>
@@ -2494,7 +2494,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F34" t="n">
         <v>0.1</v>
@@ -2509,7 +2509,7 @@
         <v>0.1</v>
       </c>
       <c r="J34" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
         <v>0.1</v>
@@ -2528,7 +2528,7 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="C35" t="n">
         <v>0.1</v>
@@ -2540,7 +2540,7 @@
         <v>0.3</v>
       </c>
       <c r="F35" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="G35" t="n">
         <v>0.1</v>
@@ -2552,7 +2552,7 @@
         <v>0.3</v>
       </c>
       <c r="J35" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="K35" t="n">
         <v>0.2</v>
@@ -2571,7 +2571,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="C36" t="n">
         <v>0.2</v>
@@ -2583,7 +2583,7 @@
         <v>0.1</v>
       </c>
       <c r="F36" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="G36" t="n">
         <v>0.1</v>
@@ -2595,10 +2595,10 @@
         <v>0.1</v>
       </c>
       <c r="J36" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="K36" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="L36" t="n">
         <v>0.1</v>
@@ -2727,7 +2727,7 @@
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L39" t="n">
         <v>0.1</v>
@@ -2767,7 +2767,7 @@
         <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
         <v>0</v>
@@ -2798,7 +2798,7 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="G41" t="n">
         <v>0.1</v>
@@ -2810,10 +2810,10 @@
         <v>0.1</v>
       </c>
       <c r="J41" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="K41" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="L41" t="n">
         <v>0.1</v>
@@ -2829,7 +2829,7 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="C42" t="n">
         <v>0.2</v>
@@ -2838,10 +2838,10 @@
         <v>0.1</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="G42" t="n">
         <v>0.6</v>
@@ -2853,7 +2853,7 @@
         <v>0.3</v>
       </c>
       <c r="J42" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="K42" t="n">
         <v>0.5</v>
@@ -2862,7 +2862,222 @@
         <v>0.4</v>
       </c>
       <c r="M42" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>هند</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="E43" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G43" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="J43" t="n">
+        <v>2</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L43" t="n">
+        <v>2</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ژاپن</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C44" t="n">
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="E44" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H44" t="n">
+        <v>1</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>افغانستان</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J45" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>اوکراین</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C46" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2</v>
+      </c>
+      <c r="E46" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F46" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H46" t="n">
+        <v>2</v>
+      </c>
+      <c r="I46" t="n">
+        <v>3</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K46" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M46" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ونزوئلا</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F47" t="n">
+        <v>8</v>
+      </c>
+      <c r="G47" t="n">
         <v>0.2</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J47" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="M47" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -19669,7 +19884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S42"/>
+  <dimension ref="A1:S47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19803,31 +20018,31 @@
         <v>0.388</v>
       </c>
       <c r="K2" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="L2" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="M2" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="N2" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="O2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q2" t="n">
         <v>3.3</v>
       </c>
-      <c r="P2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3.5</v>
-      </c>
       <c r="R2" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="S2" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="3">
@@ -19864,31 +20079,31 @@
         <v>0.17</v>
       </c>
       <c r="K3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q3" t="n">
         <v>2.1</v>
       </c>
-      <c r="L3" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="M3" t="n">
-        <v>2</v>
-      </c>
-      <c r="N3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="O3" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.3</v>
-      </c>
       <c r="R3" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="S3" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="4">
@@ -19925,31 +20140,31 @@
         <v>0.239</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="M4" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="N4" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="O4" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P4" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q4" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R4" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="S4" t="n">
         <v>2.6</v>
-      </c>
-      <c r="R4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.8</v>
       </c>
     </row>
     <row r="5">
@@ -19986,31 +20201,31 @@
         <v>0.303</v>
       </c>
       <c r="K5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L5" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P5" t="n">
         <v>2.6</v>
       </c>
-      <c r="L5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M5" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N5" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="O5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R5" t="n">
         <v>2.8</v>
       </c>
-      <c r="Q5" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="R5" t="n">
-        <v>3</v>
-      </c>
       <c r="S5" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="6">
@@ -20059,10 +20274,10 @@
         <v>0.3</v>
       </c>
       <c r="O6" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="Q6" t="n">
         <v>0.3</v>
@@ -20108,31 +20323,31 @@
         <v>0.338</v>
       </c>
       <c r="K7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O7" t="n">
         <v>2.8</v>
       </c>
-      <c r="L7" t="n">
+      <c r="P7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R7" t="n">
         <v>2.5</v>
       </c>
-      <c r="M7" t="n">
-        <v>4</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3</v>
-      </c>
-      <c r="P7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.7</v>
-      </c>
       <c r="S7" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="8">
@@ -20169,31 +20384,31 @@
         <v>0.488</v>
       </c>
       <c r="K8" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L8" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="M8" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="N8" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="O8" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="P8" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="Q8" t="n">
         <v>4.8</v>
       </c>
-      <c r="P8" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>5.1</v>
-      </c>
       <c r="R8" t="n">
-        <v>7.1</v>
+        <v>6.7</v>
       </c>
       <c r="S8" t="n">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="9">
@@ -20230,31 +20445,31 @@
         <v>0.126</v>
       </c>
       <c r="K9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="M9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P9" t="n">
         <v>1.5</v>
       </c>
-      <c r="L9" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.6</v>
-      </c>
       <c r="Q9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="10">
@@ -20291,31 +20506,31 @@
         <v>0.16</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="L10" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
       <c r="M10" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N10" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="P10" t="n">
         <v>1.9</v>
       </c>
-      <c r="N10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2</v>
-      </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="R10" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="S10" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="11">
@@ -20352,31 +20567,31 @@
         <v>0.186</v>
       </c>
       <c r="K11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M11" t="n">
+        <v>2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="O11" t="n">
         <v>2.9</v>
       </c>
-      <c r="L11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="M11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="N11" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O11" t="n">
-        <v>3.1</v>
-      </c>
       <c r="P11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R11" t="n">
         <v>3.5</v>
       </c>
-      <c r="Q11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R11" t="n">
-        <v>3.7</v>
-      </c>
       <c r="S11" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -20419,25 +20634,25 @@
         <v>0.9</v>
       </c>
       <c r="M12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Q12" t="n">
         <v>0.9</v>
       </c>
-      <c r="N12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="O12" t="n">
+      <c r="R12" t="n">
         <v>0.8</v>
       </c>
-      <c r="P12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.9</v>
-      </c>
       <c r="S12" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="13">
@@ -20474,31 +20689,31 @@
         <v>0.616</v>
       </c>
       <c r="K13" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="L13" t="n">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
       <c r="M13" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="N13" t="n">
-        <v>8.699999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="O13" t="n">
-        <v>7.9</v>
+        <v>7.4</v>
       </c>
       <c r="P13" t="n">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>7.8</v>
+        <v>7.3</v>
       </c>
       <c r="R13" t="n">
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
       <c r="S13" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="14">
@@ -20535,10 +20750,10 @@
         <v>0.028</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="L14" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M14" t="n">
         <v>0.3</v>
@@ -20547,7 +20762,7 @@
         <v>0.3</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="P14" t="n">
         <v>0.6</v>
@@ -20596,10 +20811,10 @@
         <v>0.073</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
         <v>0.8</v>
@@ -20608,16 +20823,16 @@
         <v>0.6</v>
       </c>
       <c r="O15" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="P15" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="S15" t="n">
         <v>0.8</v>
@@ -20657,31 +20872,31 @@
         <v>0.126</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
       <c r="L16" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="M16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R16" t="n">
         <v>1.5</v>
       </c>
-      <c r="N16" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O16" t="n">
-        <v>2</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.6</v>
-      </c>
       <c r="S16" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="17">
@@ -20718,31 +20933,31 @@
         <v>0.226</v>
       </c>
       <c r="K17" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="L17" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="M17" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="N17" t="n">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="O17" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="Q17" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="R17" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="S17" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="18">
@@ -20779,31 +20994,31 @@
         <v>0.065</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="L18" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="N18" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="O18" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Q18" t="n">
         <v>0.8</v>
       </c>
       <c r="R18" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="S18" t="n">
         <v>0.7</v>
-      </c>
-      <c r="S18" t="n">
-        <v>0.8</v>
       </c>
     </row>
     <row r="19">
@@ -20840,31 +21055,31 @@
         <v>0.443</v>
       </c>
       <c r="K19" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
       <c r="L19" t="n">
-        <v>8.699999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="M19" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="N19" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="O19" t="n">
-        <v>6.9</v>
+        <v>6.4</v>
       </c>
       <c r="P19" t="n">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="R19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S19" t="n">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="20">
@@ -20901,31 +21116,31 @@
         <v>1.052</v>
       </c>
       <c r="K20" t="n">
-        <v>13.9</v>
+        <v>12.8</v>
       </c>
       <c r="L20" t="n">
-        <v>15.2</v>
+        <v>14.2</v>
       </c>
       <c r="M20" t="n">
-        <v>12.3</v>
+        <v>11.3</v>
       </c>
       <c r="N20" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="O20" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="P20" t="n">
+        <v>15.7</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="R20" t="n">
         <v>12</v>
       </c>
-      <c r="O20" t="n">
-        <v>13.8</v>
-      </c>
-      <c r="P20" t="n">
-        <v>16.8</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="R20" t="n">
-        <v>12.8</v>
-      </c>
       <c r="S20" t="n">
-        <v>12.3</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="21">
@@ -20962,31 +21177,31 @@
         <v>0.284</v>
       </c>
       <c r="K21" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="L21" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P21" t="n">
         <v>2.8</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="S21" t="n">
         <v>3</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3.3</v>
       </c>
     </row>
     <row r="22">
@@ -21023,31 +21238,31 @@
         <v>0.695</v>
       </c>
       <c r="K22" t="n">
-        <v>7.1</v>
+        <v>6.6</v>
       </c>
       <c r="L22" t="n">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="M22" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
       <c r="N22" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="O22" t="n">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="P22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="Q22" t="n">
         <v>5.6</v>
       </c>
-      <c r="Q22" t="n">
-        <v>5.9</v>
-      </c>
       <c r="R22" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="S22" t="n">
-        <v>8.1</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="23">
@@ -21084,31 +21299,31 @@
         <v>0.509</v>
       </c>
       <c r="K23" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L23" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="M23" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="N23" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="O23" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="P23" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="24">
@@ -21145,7 +21360,7 @@
         <v>0.029</v>
       </c>
       <c r="K24" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="L24" t="n">
         <v>0.5</v>
@@ -21154,10 +21369,10 @@
         <v>0.3</v>
       </c>
       <c r="N24" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="O24" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="P24" t="n">
         <v>0.9</v>
@@ -21206,22 +21421,22 @@
         <v>0.074</v>
       </c>
       <c r="K25" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="L25" t="n">
         <v>0.8</v>
       </c>
       <c r="M25" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1</v>
+      </c>
+      <c r="O25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="P25" t="n">
         <v>0.9</v>
-      </c>
-      <c r="N25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="O25" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="P25" t="n">
-        <v>1</v>
       </c>
       <c r="Q25" t="n">
         <v>0.8</v>
@@ -21230,7 +21445,7 @@
         <v>0.8</v>
       </c>
       <c r="S25" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="26">
@@ -21267,31 +21482,31 @@
         <v>0.583</v>
       </c>
       <c r="K26" t="n">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="L26" t="n">
+        <v>4</v>
+      </c>
+      <c r="M26" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="N26" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O26" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P26" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="Q26" t="n">
         <v>4.3</v>
       </c>
-      <c r="M26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="N26" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="O26" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="P26" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>4.5</v>
-      </c>
       <c r="R26" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="S26" t="n">
-        <v>6.8</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="27">
@@ -21328,31 +21543,31 @@
         <v>0.134</v>
       </c>
       <c r="K27" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="L27" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="M27" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="N27" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="O27" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="P27" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
         <v>1.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="S27" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="28">
@@ -21389,31 +21604,31 @@
         <v>0.348</v>
       </c>
       <c r="K28" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="L28" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="M28" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="N28" t="n">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="O28" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="P28" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R28" t="n">
         <v>2.6</v>
       </c>
-      <c r="R28" t="n">
-        <v>2.8</v>
-      </c>
       <c r="S28" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="29">
@@ -21450,31 +21665,31 @@
         <v>0.263</v>
       </c>
       <c r="K29" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="L29" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="M29" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="N29" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="O29" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="P29" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
       <c r="Q29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="R29" t="n">
         <v>2.6</v>
       </c>
-      <c r="R29" t="n">
+      <c r="S29" t="n">
         <v>2.8</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.1</v>
       </c>
     </row>
     <row r="30">
@@ -21511,31 +21726,31 @@
         <v>0.204</v>
       </c>
       <c r="K30" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="L30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R30" t="n">
         <v>1.8</v>
       </c>
-      <c r="M30" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="N30" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O30" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.9</v>
-      </c>
       <c r="S30" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="31">
@@ -21572,16 +21787,16 @@
         <v>0.067</v>
       </c>
       <c r="K31" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="L31" t="n">
         <v>0.6</v>
       </c>
       <c r="M31" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="N31" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="O31" t="n">
         <v>0.7</v>
@@ -21590,13 +21805,13 @@
         <v>0.6</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="R31" t="n">
         <v>0.5</v>
       </c>
       <c r="S31" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="32">
@@ -21633,31 +21848,31 @@
         <v>0.08799999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="L32" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="M32" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="N32" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="O32" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="P32" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="R32" t="n">
         <v>1.2</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="33">
@@ -21755,10 +21970,10 @@
         <v>0.005</v>
       </c>
       <c r="K34" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
         <v>0.1</v>
@@ -21767,7 +21982,7 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
         <v>0.1</v>
@@ -21819,7 +22034,7 @@
         <v>0.4</v>
       </c>
       <c r="L35" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="M35" t="n">
         <v>0.3</v>
@@ -21831,7 +22046,7 @@
         <v>0.4</v>
       </c>
       <c r="P35" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="Q35" t="n">
         <v>0.5</v>
@@ -22072,7 +22287,7 @@
         <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
         <v>0</v>
@@ -22246,7 +22461,7 @@
         <v>0.1</v>
       </c>
       <c r="L42" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="M42" t="n">
         <v>0.4</v>
@@ -22264,10 +22479,315 @@
         <v>0.5</v>
       </c>
       <c r="R42" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="S42" t="n">
         <v>0.4</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>هند</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.175</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.151</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.135</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="K43" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M43" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="N43" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P43" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1.8</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ژاپن</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="K44" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N44" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>افغانستان</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="C45" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>اوکراین</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="C46" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.152</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.171</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L46" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M46" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O46" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ونزوئلا</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="C47" t="n">
+        <v>0.147</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.177</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.181</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.198</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.162</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="K47" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L47" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M47" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R47" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="S47" t="n">
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>
